--- a/data/CS1/case18_1/case18_operational_data.xlsx
+++ b/data/CS1/case18_1/case18_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case18/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case18_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD08483-5A71-E844-8847-05F3B51DB09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A070AFCF-F2A4-F54F-8E2B-5E1884FE5B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,7 +454,8 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.2</v>
+        <f>E2*3</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C2" s="1">
         <v>0.12</v>
@@ -475,13 +476,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.4</v>
+        <f t="shared" ref="B3:B16" si="0">E3*3</f>
+        <v>1.2000000000000002</v>
       </c>
       <c r="C3" s="1">
         <v>0.25</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D16" si="0">$B3/SUM($B$2:$B$1048576)</f>
+        <f t="shared" ref="D3:D16" si="1">$B3/SUM($B$2:$B$1048576)</f>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E3" s="1">
@@ -496,14 +498,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1.5</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="C4" s="1">
         <v>0.93</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="0"/>
-        <v>0.12931034482758622</v>
+        <f t="shared" si="1"/>
+        <v>0.12931034482758619</v>
       </c>
       <c r="E4" s="1">
         <v>1.5</v>
@@ -517,14 +520,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>2.2599999999999998</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.25862068965517243</v>
+        <f t="shared" si="1"/>
+        <v>0.25862068965517238</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -538,13 +542,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C6" s="1">
         <v>0.5</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="E6" s="1">
@@ -559,13 +564,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C7" s="1">
         <v>0.12</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E7" s="1">
@@ -580,14 +586,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>0.62</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>8.6206896551724144E-2</v>
+        <f t="shared" si="1"/>
+        <v>8.620689655172413E-2</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -601,14 +608,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>1.5</v>
       </c>
       <c r="C9" s="1">
         <v>0.31</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>4.3103448275862072E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.3103448275862065E-2</v>
       </c>
       <c r="E9" s="1">
         <v>0.5</v>
@@ -622,14 +630,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <v>0.62</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>8.6206896551724144E-2</v>
+        <f t="shared" si="1"/>
+        <v>8.620689655172413E-2</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -643,14 +652,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0.3</v>
+        <f t="shared" si="0"/>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C11" s="1">
         <v>0.19</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>2.5862068965517241E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.5862068965517234E-2</v>
       </c>
       <c r="E11" s="1">
         <v>0.3</v>
@@ -664,13 +674,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C12" s="1">
         <v>0.12</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E12" s="1">
@@ -685,13 +696,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>2.4000000000000004</v>
       </c>
       <c r="C13" s="1">
         <v>0.5</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="E13" s="1">
@@ -706,14 +718,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>1.5</v>
       </c>
       <c r="C14" s="1">
         <v>0.31</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>4.3103448275862072E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.3103448275862065E-2</v>
       </c>
       <c r="E14" s="1">
         <v>0.5</v>
@@ -727,14 +740,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <v>0.62</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>8.6206896551724144E-2</v>
+        <f t="shared" si="1"/>
+        <v>8.620689655172413E-2</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -748,13 +762,14 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C16" s="1">
         <v>0.12</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E16" s="1">
